--- a/artfynd/A 23568-2023 artfynd.xlsx
+++ b/artfynd/A 23568-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 23568-2023 artfynd.xlsx
+++ b/artfynd/A 23568-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>82193369</v>
       </c>
       <c r="B2" t="n">
-        <v>88856</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91333</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -705,7 +700,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
+          <t>Pers., nom.sanct.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -726,10 +721,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>575140.1725849477</v>
+        <v>575140</v>
       </c>
       <c r="R2" t="n">
-        <v>6536170.878547315</v>
+        <v>6536171</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -759,19 +754,9 @@
           <t>2020-02-14</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2020-02-14</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -806,6 +791,240 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>94142540</v>
+      </c>
+      <c r="B3" t="n">
+        <v>110078</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Trångsund, svinrot 450 m o, Srm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>575209</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6536221</v>
+      </c>
+      <c r="S3" t="n">
+        <v>25</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Katrineholm</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Stora Malm</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>D-Kat-0562</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2021-06-05</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2021-06-05</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>vägslänt</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Bo Karlsson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Bo Karlsson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>116255613</v>
+      </c>
+      <c r="B4" t="n">
+        <v>106244</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Ändbäckkärret, Ändbäckkärret, Srm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>575239</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6536225</v>
+      </c>
+      <c r="S4" t="n">
+        <v>20</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Katrineholm</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Stora Malm</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-04-26</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-04-26</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Fredrik Enoksson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Fredrik Enoksson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 23568-2023 artfynd.xlsx
+++ b/artfynd/A 23568-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -791,6 +796,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82193369</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -928,6 +938,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94142540</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1025,8 +1040,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116255613</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>